--- a/backend/files/Biblio/BooksWV.xlsx
+++ b/backend/files/Biblio/BooksWV.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\APPS\SIMPLE\Exact_v103 - New xlsx Books\backend\files\Biblio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED795207-1D34-4A05-8279-65E058DB29E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50F1F77E-6CC7-4772-9997-7BFE58BDED3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="46296" windowHeight="25416" xr2:uid="{8C43181E-41E2-4285-98AA-22B67AB52120}"/>
   </bookViews>
@@ -50,147 +50,90 @@
     <t>revisor Alexander Steiner; 232 p.; 100 caps.; 15 E-mails; 103 enus.; 1 foto; 1 microbiografia; 123 questionamentos; 2 websites; 14 refs.; alf.; 21 x 14 cm; br.; Instituto Internacional de Projeciologia e Conscienciologia (IIPC); Rio de Janeiro, RJ</t>
   </si>
   <si>
-    <t>**Vieira**, Waldo; ***100 Testes da Conscienciometria***; *Livro*; revisor Alexander Steiner; 232 p.; 100 caps.; 15 E-mails; 103 enus.; 1 foto; 1 microbiografia; 123 questionamentos; 2 websites; 14 refs.; alf.; 21 x 14 cm; br.; Instituto Internacional de Projeciologia e Conscienciologia (IIPC); Rio de Janeiro, RJ; 1997</t>
-  </si>
-  <si>
     <t>revisores Alexander Steiner; et al.; 260 p.; 200 caps.; 15 E-mails; 8 enus.; 1 foto; 1 microbiografia; 2 websites; 13 refs.; alf.; 21 x 14 cm; br.; Instituto Internacional de Projeciologia e Conscienciologia (IIPC); Rio de Janeiro, RJ</t>
   </si>
   <si>
-    <t>**Vieira**, Waldo; ***200 Teáticas da Conscienciologia: Especialidades e Subcampos***; *Livro*; revisores Alexander Steiner; et al.; 260 p.; 200 caps.; 15 E-mails; 8 enus.; 1 foto; 1 microbiografia; 2 websites; 13 refs.; alf.; 21 x 14 cm; br.; Instituto Internacional de Projeciologia e Conscienciologia (IIPC); Rio de Janeiro, RJ; 1997</t>
-  </si>
-  <si>
     <t>700 Experimentos da Conscienciologia</t>
   </si>
   <si>
     <t>revisores Ana Maria Bonfim; Everton Santos; &amp; Tatiana Lopes; 1.088 p.; 40 seções; 100 subseções; 700 caps.; 147 abrevs.; 1 blog; 1 cronologia; 100 datas; 20 E-mails; 600 enus.; 272 estrangeirismos; 1 fórmula; 1 foto; 1 microbiografia; 56 tabs.; 57 técnicas; 300 testes; 21 websites; glos. 280 termos; 5.116 refs.; alf.; geo.; ono.; 28,5 x 21,5 x 7 cm; enc.; 3ª Ed. rev. e amp.; Associação Internacional Editares; Foz do Iguaçu, PR</t>
   </si>
   <si>
-    <t>**Vieira**, Waldo; ***700 Experimentos da Conscienciologia***; *Livro*; revisores Ana Maria Bonfim; Everton Santos; &amp; Tatiana Lopes; 1.088 p.; 40 seções; 100 subseções; 700 caps.; 147 abrevs.; 1 blog; 1 cronologia; 100 datas; 20 E-mails; 600 enus.; 272 estrangeirismos; 1 fórmula; 1 foto; 1 microbiografia; 56 tabs.; 57 técnicas; 300 testes; 21 websites; glos. 280 termos; 5.116 refs.; alf.; geo.; ono.; 28,5 x 21,5 x 7 cm; enc.; 3ª Ed. rev. e amp.; Associação Internacional Editares; Foz do Iguaçu, PR; 2013</t>
-  </si>
-  <si>
     <t>revisor Alexander Steiner; 344 p.; 150 abrevs.; 106 assuntos das folhas de avaliação; 3 E-mails; 11 enus.; 100 folhas de avaliação; 1 foto; 1 microbiografia; 100 qualidades da consciência; 2.000 questionamentos; 100 títulos das folhas de avaliação; 1 website; glos. 282 termos; 7 refs.; alf.; 21 x 14 cm; br.; Instituto Internacional de Projeciologia; Rio de Janeiro, RJ</t>
   </si>
   <si>
-    <t>**Vieira**, Waldo; ***Conscienciograma: Técnica de Avaliação da Consciência Integral***; *Livro*; revisor Alexander Steiner; 344 p.; 150 abrevs.; 106 assuntos das folhas de avaliação; 3 E-mails; 11 enus.; 100 folhas de avaliação; 1 foto; 1 microbiografia; 100 qualidades da consciência; 2.000 questionamentos; 100 títulos das folhas de avaliação; 1 website; glos. 282 termos; 7 refs.; alf.; 21 x 14 cm; br.; Instituto Internacional de Projeciologia; Rio de Janeiro, RJ; 1996</t>
-  </si>
-  <si>
     <t>Dicionário de Argumentos da Conscienciologia</t>
   </si>
   <si>
     <t>revisores Equipe de Revisores do Holociclo; 1.572 p.; 1 blog; 21 E-mails; 551 enus.; 1 esquema da evolução consciencial; 18 fotos; glos. 650 termos; 19 websites; alf.; 28,5 x 21,5 x 7 cm; enc.; Associação Internacional Editares; Foz do Iguaçu, PR</t>
   </si>
   <si>
-    <t>**Vieira**, Waldo; ***Dicionário de Argumentos da Conscienciologia***; *Livro*; revisores Equipe de Revisores do Holociclo; 1.572 p.; 1 blog; 21 E-mails; 551 enus.; 1 esquema da evolução consciencial; 18 fotos; glos. 650 termos; 19 websites; alf.; 28,5 x 21,5 x 7 cm; enc.; Associação Internacional Editares; Foz do Iguaçu, PR; 2014</t>
-  </si>
-  <si>
     <t>Dicionário de Neologismos da Conscienciologia</t>
   </si>
   <si>
     <t>Lourdes Pinheiro; Org.; revisores Ernani Brito; et al.; 1.072 p.; 1 blog; 21 E-mails; 4.053 enus.; 1 facebook; 2 fotos; glos. 2.019 termos; 14.100 (termos neológicos); 1 listagem de neologismos; 1 microbiografia; 21 websites; 61 refs.; 28,5 x 21,5 x 7 cm; enc.; Associação Internacional Editares; Foz do Iguaçu, PR</t>
   </si>
   <si>
-    <t>**Vieira**, Waldo; ***Dicionário de Neologismos da Conscienciologia***; *Livro*; Lourdes Pinheiro; Org.; revisores Ernani Brito; et al.; 1.072 p.; 1 blog; 21 E-mails; 4.053 enus.; 1 facebook; 2 fotos; glos. 2.019 termos; 14.100 (termos neológicos); 1 listagem de neologismos; 1 microbiografia; 21 websites; 61 refs.; 28,5 x 21,5 x 7 cm; enc.; Associação Internacional Editares; Foz do Iguaçu, PR; 2014</t>
-  </si>
-  <si>
     <t>Homo sapiens pacificus</t>
   </si>
   <si>
     <t>revisores Equipe de Revisores do Holociclo; 1.584 p.; 24 seções; 413 caps.; 403 abrevs.; 38 E-mails; 434 enus.; 484 estrangeirismos; 1 foto; 37 ilus.; 168 megapensenes trivocabulares; 1 mi-crobiografia; 36 tabs.; 15 websites; glos. 241 termos; 25 pinacografias; 103 musicografias; 24 discografias; 20 cenografias; 240 filmes; 9.625 refs.; alf.; geo.; ono.; 29 x 21,5 x 7 cm; enc.; 3ª Ed. Gratuita; Centro de Altos Estudos da Conscienciologia (CEAEC); &amp; Associação Internacional Editares; Foz do Iguaçu, PR</t>
   </si>
   <si>
-    <t>**Vieira**, Waldo; ***Homo sapiens pacificus***; *Livro*; revisores Equipe de Revisores do Holociclo; 1.584 p.; 24 seções; 413 caps.; 403 abrevs.; 38 E-mails; 434 enus.; 484 estrangeirismos; 1 foto; 37 ilus.; 168 megapensenes trivocabulares; 1 mi-crobiografia; 36 tabs.; 15 websites; glos. 241 termos; 25 pinacografias; 103 musicografias; 24 discografias; 20 cenografias; 240 filmes; 9.625 refs.; alf.; geo.; ono.; 29 x 21,5 x 7 cm; enc.; 3ª Ed. Gratuita; Centro de Altos Estudos da Conscienciologia (CEAEC); &amp; Associação Internacional Editares; Foz do Iguaçu, PR; 2007</t>
-  </si>
-  <si>
     <t>Homo sapiens reurbanisatus</t>
   </si>
   <si>
     <t>revisores Equipe de Revisores do Holociclo; 1.584 p.; 24 seções; 479 caps.; 139 abrevs.; 12 E-mails; 597 enus.; 413 estrangeirismos; 1 foto; 40 ilus.; 1 microbiografia; 25 tabs.; 4 websites; glos. 241 termos; 3 infográficos; 102 filmes; 7.665 refs.; alf.; geo.; ono.; 29 x 21 x 7 cm; enc.; 3ª Ed. Gratuita; Centro de Altos Estudos da Conscienciologia (CEAEC); Foz do Iguaçu, PR</t>
   </si>
   <si>
-    <t>**Vieira**, Waldo; ***Homo sapiens reurbanisatus***; *Livro*; revisores Equipe de Revisores do Holociclo; 1.584 p.; 24 seções; 479 caps.; 139 abrevs.; 12 E-mails; 597 enus.; 413 estrangeirismos; 1 foto; 40 ilus.; 1 microbiografia; 25 tabs.; 4 websites; glos. 241 termos; 3 infográficos; 102 filmes; 7.665 refs.; alf.; geo.; ono.; 29 x 21 x 7 cm; enc.; 3ª Ed. Gratuita; Centro de Altos Estudos da Conscienciologia (CEAEC); Foz do Iguaçu, PR; 2004</t>
-  </si>
-  <si>
     <t>revisores Equipe de Revisores do Holociclo; 2 Vols.; 1.800 p.; Vols. 1 e 2; 1 blog; 652 conceitos analógicos; 22 E-mails; 19 enus.; 1 esquema da evolução consciencial; 17 fotos; glos. 6.476 termos; 1. 811 megapensenes trivocabulares; 1 microbiografia; 20.800 ortopensatas; 2 tabs.; 120 técnicas lexicográficas; 19 websites; 28,5 x 22 x 10 cm; enc.; Associação Internacional Editares; Foz do Iguaçu, PR</t>
   </si>
   <si>
-    <t>**Vieira**, Waldo; ***Léxico de Ortopensatas***; *Livro*; revisores Equipe de Revisores do Holociclo; 2 Vols.; 1.800 p.; Vols. 1 e 2; 1 blog; 652 conceitos analógicos; 22 E-mails; 19 enus.; 1 esquema da evolução consciencial; 17 fotos; glos. 6.476 termos; 1. 811 megapensenes trivocabulares; 1 microbiografia; 20.800 ortopensatas; 2 tabs.; 120 técnicas lexicográficas; 19 websites; 28,5 x 22 x 10 cm; enc.; Associação Internacional Editares; Foz do Iguaçu, PR; 2014</t>
-  </si>
-  <si>
     <t>revisores Equipe de Revisores do Holociclo, CEAEC &amp; EDITARES; 3 Vols.; 2.084 p.; Vol. I; 1 blog; 652 conceitos analógicos; 22 E-mails; 19 enus.; 1 esquema da evolução consciencial; 17 fotos; glos. 7.518 termos; 1.811 megapensenes trivocabulares; 1 microbiografia; 25.183 ortopensatas; 2 tabs.; 120 técnicas lexicográficas; 19 websites; 28,5 x 22 x 13cm; enc.; 2ª Ed. rev. e aum.; Associação Internacional Editares; Foz do Iguaçu, PR</t>
   </si>
   <si>
-    <t>**Vieira**, Waldo; ***Léxico de Ortopensatas***; *Livro*; revisores Equipe de Revisores do Holociclo, CEAEC &amp; EDITARES; 3 Vols.; 2.084 p.; Vol. I; 1 blog; 652 conceitos analógicos; 22 E-mails; 19 enus.; 1 esquema da evolução consciencial; 17 fotos; glos. 7.518 termos; 1.811 megapensenes trivocabulares; 1 microbiografia; 25.183 ortopensatas; 2 tabs.; 120 técnicas lexicográficas; 19 websites; 28,5 x 22 x 13cm; enc.; 2ª Ed. rev. e aum.; Associação Internacional Editares; Foz do Iguaçu, PR; 2019</t>
-  </si>
-  <si>
     <t>Manual da Dupla Evolutiva</t>
   </si>
   <si>
     <t>revisores Erotides Louly; &amp; Helena Araújo; 208 p.; 40 caps.; 20 E-mails; 88 enus.; 1 foto; 1 microbiografia; 1 teste; 17 websites; 16 refs.; alf.; 21 x 14 cm; br.; 3ª Ed.; Associação Internacional Editares; Foz do Iguaçu, PR</t>
   </si>
   <si>
-    <t>**Vieira**, Waldo; ***Manual da Dupla Evolutiva***; *Livro*; revisores Erotides Louly; &amp; Helena Araújo; 208 p.; 40 caps.; 20 E-mails; 88 enus.; 1 foto; 1 microbiografia; 1 teste; 17 websites; 16 refs.; alf.; 21 x 14 cm; br.; 3ª Ed.; Associação Internacional Editares; Foz do Iguaçu, PR; 2012</t>
-  </si>
-  <si>
     <t>revisores Erotides Louly; &amp; Helena Araújo; 164 p.; 40 caps.; 18 E-mails; 86 enus.; 1 foto; 1 microbiografia; 16 websites; 17 refs.; alf.; 21 x 14 cm; br.; 5ª Ed. rev.; Associação Internacional Editares; Foz do Iguaçu, PR</t>
   </si>
   <si>
-    <t>**Vieira**, Waldo; ***Manual da Proéxis: Programação Existencial***; *Livro*; revisores Erotides Louly; &amp; Helena Araújo; 164 p.; 40 caps.; 18 E-mails; 86 enus.; 1 foto; 1 microbiografia; 16 websites; 17 refs.; alf.; 21 x 14 cm; br.; 5ª Ed. rev.; Associação Internacional Editares; Foz do Iguaçu, PR; 2011</t>
-  </si>
-  <si>
     <t>revisores Erotides Louly; Helena Araújo; &amp; Julieta Mendonça; 154 p.; 34 caps.; 147 abrevs.; 18 E-mails; 52 enus.; 1 foto; 1 microbiografia; 1 tab.; 1 teste; 19 websites; glos. 282 termos; 5 refs.; alf.; 21 x 14 cm; br.; 3ª Ed.; Associação Internacional Editares; Foz do Iguaçu, PR</t>
   </si>
   <si>
-    <t>**Vieira**, Waldo; ***Manual da Tenepes: Tarefa Energética Pessoal***; *Livro*; revisores Erotides Louly; Helena Araújo; &amp; Julieta Mendonça; 154 p.; 34 caps.; 147 abrevs.; 18 E-mails; 52 enus.; 1 foto; 1 microbiografia; 1 tab.; 1 teste; 19 websites; glos. 282 termos; 5 refs.; alf.; 21 x 14 cm; br.; 3ª Ed.; Associação Internacional Editares; Foz do Iguaçu, PR; 2011</t>
-  </si>
-  <si>
     <t>Manual de Redação da Conscienciologia</t>
   </si>
   <si>
     <t>revisores Alexander Steiner; et al.; 276 p.; 15 seções; 150 caps.; 152 abrevs.; 23 E-mails; 54 enus.; 274 estrangeirismos; 30 expressões idiomáticas portuguesas; 1 foto; 60 locuções do idioma espanhol; 85 megapensenes trivocabulares; 1 microbiografia; 30 pesquisas; 6 técnicas; 30 teorias; 8 testes; 60 tipos de artefatos do saber; 60 vozes de animais subumanos; 3 websites; glos. 300 termos; 609 refs.; 28 x 21 cm; br.; 2a Ed. rev.; Centro de Altos Estudos da Conscienciologia (CEAEC); Foz do Iguaçu, PR</t>
   </si>
   <si>
-    <t>**Vieira**, Waldo; ***Manual de Redação da Conscienciologia***; *Livro*; revisores Alexander Steiner; et al.; 276 p.; 15 seções; 150 caps.; 152 abrevs.; 23 E-mails; 54 enus.; 274 estrangeirismos; 30 expressões idiomáticas portuguesas; 1 foto; 60 locuções do idioma espanhol; 85 megapensenes trivocabulares; 1 microbiografia; 30 pesquisas; 6 técnicas; 30 teorias; 8 testes; 60 tipos de artefatos do saber; 60 vozes de animais subumanos; 3 websites; glos. 300 termos; 609 refs.; 28 x 21 cm; br.; 2a Ed. rev.; Centro de Altos Estudos da Conscienciologia (CEAEC); Foz do Iguaçu, PR; 2002</t>
-  </si>
-  <si>
     <t>Manual dos Megapensenes Trivocabulares</t>
   </si>
   <si>
     <t>revisores Adriana Lopes; Antonio Pitaguari; &amp; Lourdes Pinheiro; 378 p.; 3 seções; 49 citações; 85 elementos linguísticos; 18 E-mails; 110 enus.; 200 fórmulas; 2 fotos; 14 ilus.; 1 microbiografia; 2 pontoações; 1 técnica; 4.672 temas; 53 variáveis; 1 verbete enciclopédico; 16 websites; glos. 12.576 termos (megapensenes trivocabulares); 9 refs.; 1 anexo; 27,5 x 21 cm; enc.; Associação Internacional Editares; Foz do Iguaçu, PR</t>
   </si>
   <si>
-    <t>**Vieira**, Waldo; ***Manual dos Megapensenes Trivocabulares***; *Livro*; revisores Adriana Lopes; Antonio Pitaguari; &amp; Lourdes Pinheiro; 378 p.; 3 seções; 49 citações; 85 elementos linguísticos; 18 E-mails; 110 enus.; 200 fórmulas; 2 fotos; 14 ilus.; 1 microbiografia; 2 pontoações; 1 técnica; 4.672 temas; 53 variáveis; 1 verbete enciclopédico; 16 websites; glos. 12.576 termos (megapensenes trivocabulares); 9 refs.; 1 anexo; 27,5 x 21 cm; enc.; Associação Internacional Editares; Foz do Iguaçu, PR; 2009</t>
-  </si>
-  <si>
     <t>Nossa Evolução</t>
   </si>
   <si>
     <t>revisora Tatiana Lopes; 170 p.; 15 caps.; 149 abrevs.; 17 E-mails; 1 foto; 1 microbiografia; 162 perguntas; 162 respostas; 13 websites; glos. 282 termos; 6 refs.; alf.; 21 x 14 cm; br.; 3ª Ed.; Associação Internacional Editares; Foz do Iguaçu, PR</t>
   </si>
   <si>
-    <t>**Vieira**, Waldo; ***Nossa Evolução***; *Livro*; revisora Tatiana Lopes; 170 p.; 15 caps.; 149 abrevs.; 17 E-mails; 1 foto; 1 microbiografia; 162 perguntas; 162 respostas; 13 websites; glos. 282 termos; 6 refs.; alf.; 21 x 14 cm; br.; 3ª Ed.; Associação Internacional Editares; Foz do Iguaçu, PR; 2010</t>
-  </si>
-  <si>
     <t>revisores Alexander Steiner; et al.; 1.254 p.; 18 seções; 525 caps.; 150 abrevs.; 17 E-mails; 1.156 enus.; 1 escala; 1 foto; 3 gráfs.; 42 ilus.; 1 microbiografia; 1 sinopse; 2 tabs.; 15 websites; glos. 300 termos; 2.041 refs.; alf.; geo.; ono.; 28 x 21 x 7 cm; enc.; 10a Ed. rev. e aum.; Associação Internacional Editares; Foz do Iguaçu, PR</t>
   </si>
   <si>
-    <t>**Vieira**, Waldo; ***Projeciologia: Panorama das Experiências da Consciência Fora do Corpo Humano***; *Livro*; revisores Alexander Steiner; et al.; 1.254 p.; 18 seções; 525 caps.; 150 abrevs.; 17 E-mails; 1.156 enus.; 1 escala; 1 foto; 3 gráfs.; 42 ilus.; 1 microbiografia; 1 sinopse; 2 tabs.; 15 websites; glos. 300 termos; 2.041 refs.; alf.; geo.; ono.; 28 x 21 x 7 cm; enc.; 10a Ed. rev. e aum.; Associação Internacional Editares; Foz do Iguaçu, PR; 2009</t>
-  </si>
-  <si>
     <t>revisoras Erotides Louly; &amp; Helena Araújo; 268 p.; 60 caps.; 60 cronologias; 1 blog; 20 E-mails; 5 enus.; 1 foto; 1 microbiografia; 1 questionário projetivo; 20 websites; glos. 24 termos; alf.; 21 x 14 cm; br.; 9ª Ed. rev.; Associação Internacional Editares; Foz do Iguaçu, PR</t>
   </si>
   <si>
-    <t>**Vieira**, Waldo; ***Projeções da Consciência: Diário de Experiências Fora do Corpo Físico***; *Livro*; revisoras Erotides Louly; &amp; Helena Araújo; 268 p.; 60 caps.; 60 cronologias; 1 blog; 20 E-mails; 5 enus.; 1 foto; 1 microbiografia; 1 questionário projetivo; 20 websites; glos. 24 termos; alf.; 21 x 14 cm; br.; 9ª Ed. rev.; Associação Internacional Editares; Foz do Iguaçu, PR; 2013</t>
-  </si>
-  <si>
     <t>Temas da Conscienciologia</t>
   </si>
   <si>
     <t>revisores Alexander Steiner; Cristiane Ferraro; &amp; Graça Razera; 232 p.; 7 seções; 90 caps.; 10 diagnósticos; 15 E-mails; 115 enus.; 1 foto; 1 microbiografia; 10 pesquisas; 30 testes conscienciométricos; 2 tabs.; 2 websites; 16 refs.; alf.; ono.; 21 x 14 cm; br.; Instituto Internacional de Projeciologia e Conscienciologia (IIPC); Rio de Janeiro, RJ</t>
   </si>
   <si>
-    <t>**Vieira**, Waldo; ***Temas da Conscienciologia***; *Livro*; revisores Alexander Steiner; Cristiane Ferraro; &amp; Graça Razera; 232 p.; 7 seções; 90 caps.; 10 diagnósticos; 15 E-mails; 115 enus.; 1 foto; 1 microbiografia; 10 pesquisas; 30 testes conscienciométricos; 2 tabs.; 2 websites; 16 refs.; alf.; ono.; 21 x 14 cm; br.; Instituto Internacional de Projeciologia e Conscienciologia (IIPC); Rio de Janeiro, RJ; 1997</t>
-  </si>
-  <si>
     <t>Instituto Internacional de Projeciologia e Conscienciologia (IIPC)</t>
   </si>
   <si>
@@ -480,6 +423,63 @@
   </si>
   <si>
     <t xml:space="preserve">verbete; *In*: **Vieira**, Waldo; Org.; ***Enciclopédia da Conscienciologia***; defendido no *Tertuliarium* do *Centro de Altos Estudos da Conscienciologia* (CEAEC); Foz do Iguaçu, PR; disponível em: &lt;https:// encyclossapiens.space/ buscaverbete&gt;; acesso em: </t>
+  </si>
+  <si>
+    <t>**Vieira**, Waldo; ***Conscienciograma: Técnica de Avaliação da Consciência Integral***; *Livro*; revisor Alexander Steiner; 344 p.; 150 abrevs.; 106 assuntos das folhas de avaliação; 3 E-mails; 11 enus.; 100 folhas de avaliação; 1 foto; 1 microbiografia; 100 qualidades da consciência; 2.000 questionamentos; 100 títulos das folhas de avaliação; 1 website; glos. 282 termos; 7 refs.; alf.; 21 x 14 cm; br.; *Instituto Internacional de Projeciologia*; Rio de Janeiro, RJ; 1996</t>
+  </si>
+  <si>
+    <t>**Vieira**, Waldo; ***100 Testes da Conscienciometria***; *Livro*; revisor Alexander Steiner; 232 p.; 100 caps.; 15 E-mails; 103 enus.; 1 foto; 1 microbiografia; 123 questionamentos; 2 websites; 14 refs.; alf.; 21 x 14 cm; br.; *Instituto Internacional de Projeciologia e Conscienciologia* (IIPC); Rio de Janeiro, RJ; 1997</t>
+  </si>
+  <si>
+    <t>**Vieira**, Waldo; ***200 Teáticas da Conscienciologia: Especialidades e Subcampos***; *Livro*; revisores Alexander Steiner; et al.; 260 p.; 200 caps.; 15 E-mails; 8 enus.; 1 foto; 1 microbiografia; 2 websites; 13 refs.; alf.; 21 x 14 cm; br.; *Instituto Internacional de Projeciologia e Conscienciologia* (IIPC); Rio de Janeiro, RJ; 1997</t>
+  </si>
+  <si>
+    <t>**Vieira**, Waldo; ***Temas da Conscienciologia***; *Livro*; revisores Alexander Steiner; Cristiane Ferraro; &amp; Graça Razera; 232 p.; 7 seções; 90 caps.; 10 diagnósticos; 15 E-mails; 115 enus.; 1 foto; 1 microbiografia; 10 pesquisas; 30 testes conscienciométricos; 2 tabs.; 2 websites; 16 refs.; alf.; ono.; 21 x 14 cm; br.; *Instituto Internacional de Projeciologia e Conscienciologia* (IIPC); Rio de Janeiro, RJ; 1997</t>
+  </si>
+  <si>
+    <t>**Vieira**, Waldo; ***Manual dos Megapensenes Trivocabulares***; *Livro*; revisores Adriana Lopes; Antonio Pitaguari; &amp; Lourdes Pinheiro; 378 p.; 3 seções; 49 citações; 85 elementos linguísticos; 18 E-mails; 110 enus.; 200 fórmulas; 2 fotos; 14 ilus.; 1 microbiografia; 2 pontoações; 1 técnica; 4.672 temas; 53 variáveis; 1 verbete enciclopédico; 16 websites; glos. 12.576 termos (megapensenes trivocabulares); 9 refs.; 1 anexo; 27,5 x 21 cm; enc.; *Associação Internacional Editares*; Foz do Iguaçu, PR; 2009</t>
+  </si>
+  <si>
+    <t>**Vieira**, Waldo; ***Projeciologia: Panorama das Experiências da Consciência Fora do Corpo Humano***; *Livro*; revisores Alexander Steiner; et al.; 1.254 p.; 18 seções; 525 caps.; 150 abrevs.; 17 E-mails; 1.156 enus.; 1 escala; 1 foto; 3 gráfs.; 42 ilus.; 1 microbiografia; 1 sinopse; 2 tabs.; 15 websites; glos. 300 termos; 2.041 refs.; alf.; geo.; ono.; 28 x 21 x 7 cm; enc.; 10a Ed. rev. e aum.; *Associação Internacional Editares*; Foz do Iguaçu, PR; 2009</t>
+  </si>
+  <si>
+    <t>**Vieira**, Waldo; ***Nossa Evolução***; *Livro*; revisora Tatiana Lopes; 170 p.; 15 caps.; 149 abrevs.; 17 E-mails; 1 foto; 1 microbiografia; 162 perguntas; 162 respostas; 13 websites; glos. 282 termos; 6 refs.; alf.; 21 x 14 cm; br.; 3ª Ed.; *Associação Internacional Editares*; Foz do Iguaçu, PR; 2010</t>
+  </si>
+  <si>
+    <t>**Vieira**, Waldo; ***Manual da Proéxis: Programação Existencial***; *Livro*; revisores Erotides Louly; &amp; Helena Araújo; 164 p.; 40 caps.; 18 E-mails; 86 enus.; 1 foto; 1 microbiografia; 16 websites; 17 refs.; alf.; 21 x 14 cm; br.; 5ª Ed. rev.; *Associação Internacional Editares*; Foz do Iguaçu, PR; 2011</t>
+  </si>
+  <si>
+    <t>**Vieira**, Waldo; ***Manual da Tenepes: Tarefa Energética Pessoal***; *Livro*; revisores Erotides Louly; Helena Araújo; &amp; Julieta Mendonça; 154 p.; 34 caps.; 147 abrevs.; 18 E-mails; 52 enus.; 1 foto; 1 microbiografia; 1 tab.; 1 teste; 19 websites; glos. 282 termos; 5 refs.; alf.; 21 x 14 cm; br.; 3ª Ed.; *Associação Internacional Editares*; Foz do Iguaçu, PR; 2011</t>
+  </si>
+  <si>
+    <t>**Vieira**, Waldo; ***Manual da Dupla Evolutiva***; *Livro*; revisores Erotides Louly; &amp; Helena Araújo; 208 p.; 40 caps.; 20 E-mails; 88 enus.; 1 foto; 1 microbiografia; 1 teste; 17 websites; 16 refs.; alf.; 21 x 14 cm; br.; 3ª Ed.; *Associação Internacional Editares*; Foz do Iguaçu, PR; 2012</t>
+  </si>
+  <si>
+    <t>**Vieira**, Waldo; ***700 Experimentos da Conscienciologia***; *Livro*; revisores Ana Maria Bonfim; Everton Santos; &amp; Tatiana Lopes; 1.088 p.; 40 seções; 100 subseções; 700 caps.; 147 abrevs.; 1 blog; 1 cronologia; 100 datas; 20 E-mails; 600 enus.; 272 estrangeirismos; 1 fórmula; 1 foto; 1 microbiografia; 56 tabs.; 57 técnicas; 300 testes; 21 websites; glos. 280 termos; 5.116 refs.; alf.; geo.; ono.; 28,5 x 21,5 x 7 cm; enc.; 3ª Ed. rev. e amp.; *Associação Internacional Editares*; Foz do Iguaçu, PR; 2013</t>
+  </si>
+  <si>
+    <t>**Vieira**, Waldo; ***Projeções da Consciência: Diário de Experiências Fora do Corpo Físico***; *Livro*; revisoras Erotides Louly; &amp; Helena Araújo; 268 p.; 60 caps.; 60 cronologias; 1 blog; 20 E-mails; 5 enus.; 1 foto; 1 microbiografia; 1 questionário projetivo; 20 websites; glos. 24 termos; alf.; 21 x 14 cm; br.; 9ª Ed. rev.; *Associação Internacional Editares*; Foz do Iguaçu, PR; 2013</t>
+  </si>
+  <si>
+    <t>**Vieira**, Waldo; ***Dicionário de Argumentos da Conscienciologia***; *Livro*; revisores Equipe de Revisores do Holociclo; 1.572 p.; 1 blog; 21 E-mails; 551 enus.; 1 esquema da evolução consciencial; 18 fotos; glos. 650 termos; 19 websites; alf.; 28,5 x 21,5 x 7 cm; enc.; *Associação Internacional Editares*; Foz do Iguaçu, PR; 2014</t>
+  </si>
+  <si>
+    <t>**Vieira**, Waldo; ***Dicionário de Neologismos da Conscienciologia***; *Livro*; Lourdes Pinheiro; Org.; revisores Ernani Brito; et al.; 1.072 p.; 1 blog; 21 E-mails; 4.053 enus.; 1 facebook; 2 fotos; glos. 2.019 termos; 14.100 (termos neológicos); 1 listagem de neologismos; 1 microbiografia; 21 websites; 61 refs.; 28,5 x 21,5 x 7 cm; enc.; *Associação Internacional Editares*; Foz do Iguaçu, PR; 2014</t>
+  </si>
+  <si>
+    <t>**Vieira**, Waldo; ***Léxico de Ortopensatas***; *Livro*; revisores Equipe de Revisores do Holociclo; 2 Vols.; 1.800 p.; Vols. 1 e 2; 1 blog; 652 conceitos analógicos; 22 E-mails; 19 enus.; 1 esquema da evolução consciencial; 17 fotos; glos. 6.476 termos; 1. 811 megapensenes trivocabulares; 1 microbiografia; 20.800 ortopensatas; 2 tabs.; 120 técnicas lexicográficas; 19 websites; 28,5 x 22 x 10 cm; enc.; *Associação Internacional Editares*; Foz do Iguaçu, PR; 2014</t>
+  </si>
+  <si>
+    <t>**Vieira**, Waldo; ***Léxico de Ortopensatas***; *Livro*; revisores Equipe de Revisores do Holociclo, CEAEC &amp; EDITARES; 3 Vols.; 2.084 p.; Vol. I; 1 blog; 652 conceitos analógicos; 22 E-mails; 19 enus.; 1 esquema da evolução consciencial; 17 fotos; glos. 7.518 termos; 1.811 megapensenes trivocabulares; 1 microbiografia; 25.183 ortopensatas; 2 tabs.; 120 técnicas lexicográficas; 19 websites; 28,5 x 22 x 13cm; enc.; 2ª Ed. rev. e aum.; *Associação Internacional Editares*; Foz do Iguaçu, PR; 2019</t>
+  </si>
+  <si>
+    <t>**Vieira**, Waldo; ***Manual de Redação da Conscienciologia***; *Livro*; revisores Alexander Steiner; et al.; 276 p.; 15 seções; 150 caps.; 152 abrevs.; 23 E-mails; 54 enus.; 274 estrangeirismos; 30 expressões idiomáticas portuguesas; 1 foto; 60 locuções do idioma espanhol; 85 megapensenes trivocabulares; 1 microbiografia; 30 pesquisas; 6 técnicas; 30 teorias; 8 testes; 60 tipos de artefatos do saber; 60 vozes de animais subumanos; 3 websites; glos. 300 termos; 609 refs.; 28 x 21 cm; br.; 2a Ed. rev.; *Centro de Altos Estudos da Conscienciologia* (CEAEC); Foz do Iguaçu, PR; 2002</t>
+  </si>
+  <si>
+    <t>**Vieira**, Waldo; ***Homo sapiens reurbanisatus***; *Livro*; revisores Equipe de Revisores do Holociclo; 1.584 p.; 24 seções; 479 caps.; 139 abrevs.; 12 E-mails; 597 enus.; 413 estrangeirismos; 1 foto; 40 ilus.; 1 microbiografia; 25 tabs.; 4 websites; glos. 241 termos; 3 infográficos; 102 filmes; 7.665 refs.; alf.; geo.; ono.; 29 x 21 x 7 cm; enc.; 3ª Ed. Gratuita; *Centro de Altos Estudos da Conscienciologia* (CEAEC); Foz do Iguaçu, PR; 2004</t>
+  </si>
+  <si>
+    <t>**Vieira**, Waldo; ***Homo sapiens pacificus***; *Livro*; revisores Equipe de Revisores do Holociclo; 1.584 p.; 24 seções; 413 caps.; 403 abrevs.; 38 E-mails; 434 enus.; 484 estrangeirismos; 1 foto; 37 ilus.; 168 megapensenes trivocabulares; 1 mi-crobiografia; 36 tabs.; 15 websites; glos. 241 termos; 25 pinacografias; 103 musicografias; 24 discografias; 20 cenografias; 240 filmes; 9.625 refs.; alf.; geo.; ono.; 29 x 21,5 x 7 cm; enc.; 3ª Ed. Gratuita; *Centro de Altos Estudos da Conscienciologia* (CEAEC); &amp; *Associação Internacional Editares*; Foz do Iguaçu, PR; 2007</t>
   </si>
 </sst>
 </file>
@@ -1106,81 +1106,81 @@
     <col min="7" max="7" width="16.77734375" customWidth="1"/>
     <col min="8" max="8" width="14.21875" customWidth="1"/>
     <col min="10" max="10" width="1" customWidth="1"/>
-    <col min="11" max="11" width="79.5546875" style="21" customWidth="1"/>
-    <col min="12" max="12" width="87.5546875" style="19" customWidth="1"/>
+    <col min="11" max="11" width="36.44140625" style="21" customWidth="1"/>
+    <col min="12" max="12" width="96.5546875" style="19" customWidth="1"/>
     <col min="13" max="13" width="40.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="C1" s="28" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="J1" s="2"/>
       <c r="K1" s="25" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="L1" s="26" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" s="9" customFormat="1" ht="32.4" x14ac:dyDescent="0.3">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" s="9" customFormat="1" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="C2" s="29" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="D2" s="22" t="s">
         <v>2</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="I2" s="7">
         <v>1996</v>
       </c>
       <c r="J2" s="8"/>
       <c r="K2" s="16" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="L2" s="17" t="s">
-        <v>11</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:12" s="9" customFormat="1" ht="21.6" x14ac:dyDescent="0.3">
@@ -1191,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>141</v>
+        <v>122</v>
       </c>
       <c r="D3" s="22" t="s">
         <v>2</v>
@@ -1200,59 +1200,59 @@
         <v>3</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="I3" s="7">
         <v>1997</v>
       </c>
       <c r="J3" s="8"/>
       <c r="K3" s="16" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="L3" s="17" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" s="9" customFormat="1" ht="32.4" x14ac:dyDescent="0.3">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" s="9" customFormat="1" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>142</v>
+        <v>123</v>
       </c>
       <c r="D4" s="22" t="s">
         <v>2</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="I4" s="7">
         <v>1997</v>
       </c>
       <c r="J4" s="8"/>
       <c r="K4" s="16" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="L4" s="17" t="s">
-        <v>6</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5" spans="1:12" s="9" customFormat="1" ht="21.6" x14ac:dyDescent="0.3">
@@ -1260,35 +1260,35 @@
         <v>0</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="D5" s="22" t="s">
         <v>2</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="I5" s="7">
         <v>1997</v>
       </c>
       <c r="J5" s="8"/>
       <c r="K5" s="16" t="s">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="L5" s="17" t="s">
-        <v>50</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" spans="1:12" s="9" customFormat="1" ht="21.6" x14ac:dyDescent="0.3">
@@ -1296,35 +1296,35 @@
         <v>0</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>130</v>
+        <v>111</v>
       </c>
       <c r="D6" s="22" t="s">
         <v>2</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="I6" s="7">
         <v>2002</v>
       </c>
       <c r="J6" s="8"/>
       <c r="K6" s="16" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="L6" s="17" t="s">
-        <v>37</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" spans="1:12" s="9" customFormat="1" ht="21.6" x14ac:dyDescent="0.3">
@@ -1332,143 +1332,143 @@
         <v>0</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C7" s="29" t="s">
-        <v>134</v>
+        <v>115</v>
       </c>
       <c r="D7" s="22" t="s">
         <v>2</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="I7" s="7">
         <v>2004</v>
       </c>
       <c r="J7" s="8"/>
       <c r="K7" s="16" t="s">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="L7" s="17" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" s="9" customFormat="1" ht="32.4" x14ac:dyDescent="0.3">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" s="9" customFormat="1" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>135</v>
+        <v>116</v>
       </c>
       <c r="D8" s="22" t="s">
         <v>2</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="I8" s="7">
         <v>2007</v>
       </c>
       <c r="J8" s="8"/>
       <c r="K8" s="16" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="L8" s="17" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" s="9" customFormat="1" ht="32.4" x14ac:dyDescent="0.3">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" s="9" customFormat="1" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="D9" s="22" t="s">
         <v>2</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="I9" s="7">
         <v>2009</v>
       </c>
       <c r="J9" s="8"/>
       <c r="K9" s="16" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="L9" s="17" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" s="9" customFormat="1" ht="32.4" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" s="9" customFormat="1" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="C10" s="29" t="s">
-        <v>124</v>
+        <v>105</v>
       </c>
       <c r="D10" s="22" t="s">
         <v>2</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="I10" s="7">
         <v>2009</v>
       </c>
       <c r="J10" s="8"/>
       <c r="K10" s="16" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="L10" s="17" t="s">
-        <v>45</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11" spans="1:12" s="9" customFormat="1" ht="21.6" x14ac:dyDescent="0.3">
@@ -1476,35 +1476,35 @@
         <v>0</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="C11" s="29" t="s">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="D11" s="22" t="s">
         <v>2</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="I11" s="7">
         <v>2010</v>
       </c>
       <c r="J11" s="8"/>
       <c r="K11" s="16" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="L11" s="17" t="s">
-        <v>43</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12" spans="1:12" s="9" customFormat="1" ht="21.6" x14ac:dyDescent="0.3">
@@ -1512,35 +1512,35 @@
         <v>0</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>98</v>
+        <v>79</v>
       </c>
       <c r="C12" s="29" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="D12" s="22" t="s">
         <v>2</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="I12" s="7">
         <v>2011</v>
       </c>
       <c r="J12" s="8"/>
       <c r="K12" s="16" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="L12" s="17" t="s">
-        <v>32</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13" spans="1:12" s="9" customFormat="1" ht="21.6" x14ac:dyDescent="0.3">
@@ -1548,35 +1548,35 @@
         <v>0</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="C13" s="29" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="D13" s="22" t="s">
         <v>2</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="I13" s="7">
         <v>2011</v>
       </c>
       <c r="J13" s="8"/>
       <c r="K13" s="16" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="L13" s="17" t="s">
-        <v>34</v>
+        <v>137</v>
       </c>
     </row>
     <row r="14" spans="1:12" s="9" customFormat="1" ht="21.6" x14ac:dyDescent="0.3">
@@ -1584,35 +1584,35 @@
         <v>0</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="C14" s="29" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="D14" s="22" t="s">
         <v>2</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="I14" s="7">
         <v>2012</v>
       </c>
       <c r="J14" s="8"/>
       <c r="K14" s="16" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="L14" s="17" t="s">
-        <v>30</v>
+        <v>138</v>
       </c>
     </row>
     <row r="15" spans="1:12" s="9" customFormat="1" ht="21.6" x14ac:dyDescent="0.3">
@@ -1620,35 +1620,35 @@
         <v>0</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C15" s="29" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="D15" s="22" t="s">
         <v>2</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="I15" s="7">
         <v>2013</v>
       </c>
       <c r="J15" s="8"/>
       <c r="K15" s="16" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="L15" s="17" t="s">
-        <v>9</v>
+        <v>139</v>
       </c>
     </row>
     <row r="16" spans="1:12" s="9" customFormat="1" ht="21.6" x14ac:dyDescent="0.3">
@@ -1656,35 +1656,35 @@
         <v>0</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="C16" s="29" t="s">
-        <v>138</v>
+        <v>119</v>
       </c>
       <c r="D16" s="22" t="s">
         <v>2</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="I16" s="7">
         <v>2013</v>
       </c>
       <c r="J16" s="8"/>
       <c r="K16" s="16" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="L16" s="17" t="s">
-        <v>47</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17" spans="1:12" s="9" customFormat="1" ht="21.6" x14ac:dyDescent="0.3">
@@ -1692,35 +1692,35 @@
         <v>0</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C17" s="29" t="s">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="D17" s="22" t="s">
         <v>2</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="I17" s="7">
         <v>2014</v>
       </c>
       <c r="J17" s="8"/>
       <c r="K17" s="16" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="L17" s="17" t="s">
-        <v>14</v>
+        <v>141</v>
       </c>
     </row>
     <row r="18" spans="1:12" s="9" customFormat="1" ht="21.6" x14ac:dyDescent="0.3">
@@ -1728,35 +1728,35 @@
         <v>0</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>136</v>
+        <v>117</v>
       </c>
       <c r="D18" s="22" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="I18" s="7">
         <v>2014</v>
       </c>
       <c r="J18" s="8"/>
       <c r="K18" s="16" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="L18" s="17" t="s">
-        <v>17</v>
+        <v>142</v>
       </c>
     </row>
     <row r="19" spans="1:12" s="9" customFormat="1" ht="21.6" x14ac:dyDescent="0.3">
@@ -1764,35 +1764,35 @@
         <v>0</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="C19" s="29" t="s">
-        <v>143</v>
+        <v>124</v>
       </c>
       <c r="D19" s="22" t="s">
         <v>2</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="I19" s="7">
         <v>2014</v>
       </c>
       <c r="J19" s="8"/>
       <c r="K19" s="16" t="s">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="L19" s="17" t="s">
-        <v>25</v>
+        <v>143</v>
       </c>
     </row>
     <row r="20" spans="1:12" s="15" customFormat="1" ht="21.6" x14ac:dyDescent="0.3">
@@ -1800,35 +1800,35 @@
         <v>0</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="C20" s="32" t="s">
-        <v>144</v>
+        <v>125</v>
       </c>
       <c r="D20" s="23" t="s">
         <v>2</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="H20" s="12" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="I20" s="13">
         <v>2019</v>
       </c>
       <c r="J20" s="14"/>
       <c r="K20" s="33" t="s">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="L20" s="18" t="s">
-        <v>27</v>
+        <v>144</v>
       </c>
     </row>
     <row r="21" spans="1:12" s="9" customFormat="1" ht="54" x14ac:dyDescent="0.3">
@@ -1836,35 +1836,35 @@
         <v>0</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="C21" s="30" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="D21" s="22" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="I21" s="7">
         <v>2023</v>
       </c>
       <c r="J21" s="8"/>
       <c r="K21" s="16" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="L21" s="27" t="s">
-        <v>145</v>
+        <v>126</v>
       </c>
     </row>
     <row r="22" spans="1:12" s="9" customFormat="1" ht="32.4" x14ac:dyDescent="0.3">
@@ -1872,31 +1872,31 @@
         <v>0</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="C22" s="30" t="s">
-        <v>140</v>
+        <v>121</v>
       </c>
       <c r="D22" s="22" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="G22" s="6"/>
       <c r="H22" s="6"/>
       <c r="I22" s="7" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="J22" s="8"/>
       <c r="K22" s="16" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="L22" s="17" t="s">
-        <v>83</v>
+        <v>64</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
